--- a/www/download/COUNTRY.USA.EXI382.xlsx
+++ b/www/download/COUNTRY.USA.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.3257</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>213.206</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>128.167</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>130.145</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>118.832</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>135.189</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>137.353</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>139.174</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>139.22</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>138.817</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>123.654</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>141.572</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>127.07</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>146.683</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>148.29</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>147.644</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>142.184</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>141.382</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>122.895</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>144.753</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>141.957</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>146.066</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>185.031</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>185.632</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>191.95</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>186.49</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>209.304</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>211.026</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>200.156</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>114.86</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>117.176</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>107.186</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>123.273</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>126.217</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>128.941</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>129.087</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>128.854</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>114.314</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>131.143</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>117.489</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>136.094</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>137.871</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>137.581</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>132.355</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>131.701</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>114.339</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>135.224</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>132.544</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>136.388</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>173.1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>173.696</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>179.721</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>174.444</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>196.205</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>197.869</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>350066.377</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>231678.3</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>235382.6</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>218699.3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>244915.7</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>248202.2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>250068.2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>247322.8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>244650.5</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>218699.6</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>246757.1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>223473.1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>254734.9</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>256939</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>254869</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>241116.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>240628.4</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>213552.3</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>248582.3</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>243602.766</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>249572.392</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>314254.632</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>314360.92</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>323303.057</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>314472.142</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>349426.941</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>350740.402</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>329500.427</t>
+          <t>424942990687.171</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>183234.3</t>
+          <t>212791095821.376</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>188225.4</t>
+          <t>236343590022.013</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>173907</t>
+          <t>214924461564.583</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>201684.3</t>
+          <t>256219384141.196</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>207681.8</t>
+          <t>267407908702.516</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>213035.8</t>
+          <t>262866268696.08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>210703.2</t>
+          <t>264920604637.927</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>209217.5</t>
+          <t>254303074746.731</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>184073.7</t>
+          <t>240425339104.371</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>210382.9</t>
+          <t>282994004206.942</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>188604.9</t>
+          <t>251783070629.659</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>217913.1</t>
+          <t>249893439027.552</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>220613</t>
+          <t>274046490090.858</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>219801</t>
+          <t>231788526981.805</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>207679.4</t>
+          <t>233085952039.338</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>207665.6</t>
+          <t>243082461820.688</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>182694.6</t>
+          <t>213025671590.004</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>216031.7</t>
+          <t>246858614672.954</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>227636.688</t>
+          <t>206659978979.994</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>233245.291</t>
+          <t>223013962856.002</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>294241.154</t>
+          <t>258789316820.049</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>294426.494</t>
+          <t>265158794685.839</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>303041.963</t>
+          <t>266386253527.737</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>294588.389</t>
+          <t>268493466205.877</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>327978.602</t>
+          <t>289986982592.919</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>329410.298</t>
+          <t>296080201275.607</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>452245322190.493</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>120073934326.371</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>123373252588.533</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>123554874356.355</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>148315189039.722</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>161684152886.591</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>176605221659.619</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>181213234177.153</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>165654854658.507</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>159208001344.976</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>183504633561.877</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>156737587710.304</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>159340768964.83</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>163615337310.271</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>162181712281.994</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>150454191385.202</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>143713825151.602</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>133100987949.762</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>151046195749.22</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>133277619761.587</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>146033207440.854</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>174574169733.922</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>169238817933.606</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>199749755938.419</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>180029649252.756</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>197182866933.967</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>214223612604.586</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11776327.6933601</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3252843.30559764</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2942925.82576691</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2706584.46299524</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2828252.2091915</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2593062.07596059</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2240342.0093396</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2431023.63215106</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2738671.07389969</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2508832.85668101</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2519445.81134649</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2309280.51440803</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2145551.59357635</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2416428.5839186</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2342016.27473151</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1957404.70867194</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2103992.64146729</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1804359.90151406</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1785368.18789208</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4855054.22202052</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3964912.41660826</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5368344.59049228</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>4582004.31502265</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5324335.10156113</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>5603613.2900475</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4169558.71245632</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6065599.18299962</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>552443.242424044</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>778780.229740451</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>856228.546681964</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>712448.43063367</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>957867.054622699</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1152048.97145324</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1161769.73736672</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1118909.02475144</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1018665.59363232</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>753487.488632467</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1073275.05964987</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>874860.574711841</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1227514.44134972</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>1243665.98413753</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1230438.71460856</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1329009.79033094</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1380350.39976139</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1086725.032022</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1532923.32780831</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1473429.33355329</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>1716356.27915546</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>1984355.61564087</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2119431.30603655</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2136479.58118797</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2294812.30404401</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2291991.35919685</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2288040.62168198</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1584018.61458792</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1617014.94952643</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1956127.0338775</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1828779.56739762</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2299644.51805518</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2868969.57273895</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2831792.98567542</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2766469.63113813</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2439473.84385841</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2253848.53740376</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2844025.15642432</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2706746.03719472</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2783291.17057733</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3066993.90515206</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2599542.89026813</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3014584.46712684</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3272937.80851247</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3165848.87609306</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3583641.38660255</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3105322.2024016</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>3785471.81954771</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>4003842.81083415</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>4337226.44103851</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>4237793.64591009</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>4550929.54574792</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>4675882.63697344</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>4687145.04684685</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.271412193612938</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.526012294241761</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.525658082694429</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.40752844358392</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.359835774783442</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.284490757394641</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.206282566268583</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.162736270100767</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.26297234349905</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.156183724718034</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.146471867856838</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.20331633755007</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.367591617736375</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.348363812504731</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.355276109169797</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.380349713676636</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.444993895200877</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.372601381959042</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.430235954824275</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.707988844247295</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.597207205095886</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.68547932381124</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.739710175921988</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.517108050179794</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.636332629527371</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.663322009292703</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.537693694128357</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2259.46482667271</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1045.39018083178</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1052.89290498887</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1152.71574298796</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1203.14024793463</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1281.00342336822</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1369.65915930212</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1403.80699975338</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1285.60118163606</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1392.72531225391</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1399.27128067734</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1334.06180757625</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1170.81406208065</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1186.72771873904</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1178.80893642255</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1136.74731884096</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1091.21286210099</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1164.09088718432</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1117.00730454083</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1005.5370486555</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1070.72245587425</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1008.51645952075</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>974.340397941219</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1111.44207074449</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1032.02176786165</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1004.98354959599</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1082.65101651783</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>423604588115.548</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3.656</t>
+          <t>86839374205.0227</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>96990699153.4473</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.743</t>
+          <t>105591874338.209</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>97854762503.7247</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.372</t>
+          <t>95325463608.0561</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.113</t>
+          <t>100524517675.733</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6.828</t>
+          <t>101654994294.7</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5.658</t>
+          <t>90151120972.9657</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>97897062029.702</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5.763</t>
+          <t>97677700756.7278</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>99394134278.9319</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>6.126</t>
+          <t>92570488351.993</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>5.754</t>
+          <t>99158622702.4713</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6.076</t>
+          <t>107215173528.382</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>106556630813.134</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>5.966</t>
+          <t>104608688733.014</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>7.262</t>
+          <t>111190642743.371</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>6.708</t>
+          <t>121239775384.156</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>98560373977.4445</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.053</t>
+          <t>108126876331.263</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>9.344</t>
+          <t>123507589403.945</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>9.729</t>
+          <t>117523795373.73</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>138032128875.887</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>10.506</t>
+          <t>128714561086.832</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>142366484215.838</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>155056380402.251</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>354064901842.042</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>91084328348.5894</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>101977897223.458</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>111710341327.147</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>105048448437.434</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>107323064097.756</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>110713023956.736</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>113251616853.599</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>104981939759.103</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>112143586935.856</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>109671931997.492</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>109916471085.54</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>97282857495.6551</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>107324682301.819</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>108809938706.839</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>108361632417.26</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>103332021999.325</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>110347725306.604</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>120283072721.003</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>96545760672.3785</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>106374326526.943</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>118227150308.392</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>119541400804.286</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>141264473630.735</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>129282315577.257</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>143051768952.714</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>142814044983.465</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>69539686273.5055</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-4244954143.56679</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-4987198070.01048</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6118466988.93747</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-7193685933.70945</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-11997600489.6997</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-10188506281.0031</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-11596622558.8985</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-14830818786.1376</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-14246524906.1543</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-11994231240.7646</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-10522336806.6077</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-4712369143.66214</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-8166059599.34804</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-1594765178.45673</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-1805001604.12541</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1276666733.68939</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>842917436.7671</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>956702663.153589</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2014613305.06607</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1752549804.32027</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>5280439095.55286</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-2017605430.55583</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-3232344754.84784</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-567754490.42438</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-685284736.876655</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>12242335418.7866</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.799</t>
+          <t>1646.21852167419</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>11.679</t>
+          <t>1595.27826822892</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.756</t>
+          <t>1606.35457070788</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.786</t>
+          <t>1622.48019562252</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16.455</t>
+          <t>1636.07315122333</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>20.522</t>
+          <t>1645.43705750737</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>21.714</t>
+          <t>1652.19596559623</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20.911</t>
+          <t>1632.25731483459</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18.304</t>
+          <t>1623.67873717605</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>17.872</t>
+          <t>1610.24633903082</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19.357</t>
+          <t>1604.22515879657</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>20.337</t>
+          <t>1605.29836835808</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>19.517</t>
+          <t>1601.19549722937</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>18.796</t>
+          <t>1600.14071124401</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>18.269</t>
+          <t>1597.61158880934</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>20.397</t>
+          <t>1569.10883608481</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>20.499</t>
+          <t>1576.79592410061</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>22.754</t>
+          <t>1597.83276047513</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>1597.58400875564</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>23.786</t>
+          <t>1717.44606158095</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>29.628</t>
+          <t>1710.16562118032</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>29.931</t>
+          <t>1699.83364024554</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>30.653</t>
+          <t>1695.06990511022</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>31.049</t>
+          <t>1686.17771283496</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>34.291</t>
+          <t>1688.73089313454</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>34.858</t>
+          <t>1671.61125702011</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>35.101</t>
+          <t>1664.78564104112</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.369</t>
+          <t>1641.91712923518</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.656</t>
+          <t>1807.62127684541</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>1808.61669014025</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4.743</t>
+          <t>1840.41211225608</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>1811.64735426959</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6.372</t>
+          <t>1807.0374822264</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7.113</t>
+          <t>1796.8025636969</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6.828</t>
+          <t>1776.48901020009</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5.658</t>
+          <t>1762.39581607498</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>1768.64153201649</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>5.763</t>
+          <t>1742.97954397805</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6.343</t>
+          <t>1758.66136775024</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.126</t>
+          <t>1736.63546559543</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>5.754</t>
+          <t>1732.67920965623</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>6.076</t>
+          <t>1726.24014521403</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>1695.80684183876</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>5.966</t>
+          <t>1701.97337709167</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>7.262</t>
+          <t>1737.68094714976</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>6.708</t>
+          <t>1717.28599752664</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>1716.03194549284</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>9.053</t>
+          <t>1708.63308617539</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>9.344</t>
+          <t>1698.39304683095</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>9.729</t>
+          <t>1693.46002225493</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>9.904</t>
+          <t>1684.30618195242</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>10.506</t>
+          <t>1686.26972424689</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10.695</t>
+          <t>1669.47422495515</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>11.255</t>
+          <t>1662.06899321405</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>762739.573143637</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>844606.42458132</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1046988.19257992</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1056260.21072063</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1159154.37872613</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1470817.39757804</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1417083.89380895</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1303341.48755848</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1111201.63471755</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1130874.5777102</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1252920.12404966</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1403379.43226381</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>1444218.45557532</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>1481802.29990326</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1336571.05445703</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1637836.75084316</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1774332.9047133</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2008455.54800601</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1994197.61022242</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2071212.07745444</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2395735.59246465</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2342626.55977028</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2441335.20365199</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2477209.29471956</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2613401.34301513</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2700811.54593076</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2797053.49711122</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>35545254952.7283</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>16791140331.305</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>21377695389.5613</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19175019804.1533</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>22181005547.1846</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>24126639218.6451</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>21775159919.3299</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21012998425.8404</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>19758329549.7615</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>21366774808.9668</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>23894766201.2004</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>24638143640.4745</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>22684356321.9438</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>27214005421.8668</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>21542971096.0314</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>23164909764.5397</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>26829151337.1998</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>28780247376.2403</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>28691811365.5699</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>23577301233.0972</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>24309379674.5077</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>26273383926.7196</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>30613946504.7662</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>27577748175.6837</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>26645099016.0161</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>30819514816.4081</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>32208126592.0753</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>852501.573390694</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>943890.610458621</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1164605.53509443</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1246096.98733569</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1473125.95478317</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2001962.26425258</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1954434.36958326</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1891778.21001696</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1692964.51802179</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1781851.37137523</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2011155.40717952</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2206477.58874169</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2129882.45833135</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2124853.134854</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1708350.45494787</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>2144878.44088322</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2318826.39557839</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2587293.39633956</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2477551.94653872</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2571036.43857401</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>3016515.13800594</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2948251.00213214</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>3084547.70587315</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>3152208.17674434</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>3326661.51228178</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>3437860.62844649</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3543913.02827846</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>350066.377</t>
+          <t>510002371536.047</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>231678.3</t>
+          <t>123798910333.818</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>235382.6</t>
+          <t>140384916389.857</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>218699.3</t>
+          <t>160531824030.805</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>244915.7</t>
+          <t>177631936209.033</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>248202.2</t>
+          <t>201854224646.676</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>250068.2</t>
+          <t>208963018829.178</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>247322.8</t>
+          <t>221133198880.068</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>244650.5</t>
+          <t>208737966122.41</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>218699.6</t>
+          <t>238646367946.517</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>246757.1</t>
+          <t>248387761110.948</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>223473.1</t>
+          <t>243526617562.637</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>254734.9</t>
+          <t>200402248884.82</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>256939</t>
+          <t>214495896207.438</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>254869</t>
+          <t>183480878785.799</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>241116.6</t>
+          <t>192240803350.745</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>240628.4</t>
+          <t>194226518229.056</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>213552.3</t>
+          <t>203082293588.249</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>248582.3</t>
+          <t>205301545173.362</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>243602.766</t>
+          <t>175272049998.243</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>249572.392</t>
+          <t>192443838394.002</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>314254.632</t>
+          <t>214011401225.15</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>314360.92</t>
+          <t>210093743444.141</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>323303.057</t>
+          <t>232697817590.9</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>314472.142</t>
+          <t>220457065624.532</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>349426.941</t>
+          <t>244710219641.497</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>350740.402</t>
+          <t>260034820670.698</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>329500.427</t>
+          <t>-89762.0002470572</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>183234.3</t>
+          <t>-99284.1858773012</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>188225.4</t>
+          <t>-117617.342514511</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>173907</t>
+          <t>-189836.77661506</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>201684.3</t>
+          <t>-313971.576057046</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>207681.8</t>
+          <t>-531144.866674539</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>213035.8</t>
+          <t>-537350.475774303</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>210703.2</t>
+          <t>-588436.722458478</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>209217.5</t>
+          <t>-581762.883304242</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>184073.7</t>
+          <t>-650976.793665033</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>210382.9</t>
+          <t>-758235.283129854</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>188604.9</t>
+          <t>-803098.156477875</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>217913.1</t>
+          <t>-685664.002756028</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>220613</t>
+          <t>-643050.834950744</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>219801</t>
+          <t>-371779.400490839</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>207679.4</t>
+          <t>-507041.690040059</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>207665.6</t>
+          <t>-544493.490865086</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>182694.6</t>
+          <t>-578837.84833355</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>216031.7</t>
+          <t>-483354.336316296</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>227636.688</t>
+          <t>-499824.361119573</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>233245.291</t>
+          <t>-620779.545541295</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>294241.154</t>
+          <t>-605624.442361861</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>294426.494</t>
+          <t>-643212.502221159</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>303041.963</t>
+          <t>-674998.882024781</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>294588.389</t>
+          <t>-713260.169266648</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>327978.602</t>
+          <t>-737049.082515732</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>329410.298</t>
+          <t>-746859.531167241</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>414846.542</t>
+          <t>-474457116583.319</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>205754.21</t>
+          <t>-107007770002.513</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>228491.465</t>
+          <t>-119007221000.296</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>206317.113</t>
+          <t>-141356804226.652</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>245210.382</t>
+          <t>-155450930661.848</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>254135.827</t>
+          <t>-177727585428.03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>249808.279</t>
+          <t>-187187858909.848</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>251271.671</t>
+          <t>-200120200454.227</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>243110.482</t>
+          <t>-188979636572.649</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>227038.177</t>
+          <t>-217279593137.55</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>269019.866</t>
+          <t>-224492994909.748</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>237153.994</t>
+          <t>-218888473922.162</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>240904.14</t>
+          <t>-177717892562.876</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>260723.562</t>
+          <t>-187281890785.572</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>222090.788</t>
+          <t>-161937907689.767</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>221878.784</t>
+          <t>-169075893586.205</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>230166.078</t>
+          <t>-167397366891.856</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>199616.021</t>
+          <t>-174302046212.009</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>234527.071</t>
+          <t>-176609733807.792</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>198466.384</t>
+          <t>-151694748765.146</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>213381.545</t>
+          <t>-168134458719.494</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>248823.763</t>
+          <t>-187738017298.431</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>254723.405</t>
+          <t>-179479796939.375</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>256542.567</t>
+          <t>-205120069415.217</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>259096.163</t>
+          <t>-193811966608.516</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>278607.041</t>
+          <t>-213890704825.089</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>283661.592</t>
+          <t>-227826694078.623</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1846857.30671829</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1994926.34293299</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>1912409.49667289</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.521</t>
+          <t>2537975.54106991</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>2823297.02553743</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.366</t>
+          <t>2896411.14827112</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.338</t>
+          <t>3679395.62032357</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.283</t>
+          <t>3540462.19432457</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2.034</t>
+          <t>2428801.33073053</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>2939912.52534229</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2.359</t>
+          <t>2458118.35130639</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3272015.96323896</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.337</t>
+          <t>3163441.92669876</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.564</t>
+          <t>2960297.19299349</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.174</t>
+          <t>3008626.20180173</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2.501</t>
+          <t>3126585.16579642</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>2.704</t>
+          <t>2393112.73147096</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>3511420.83112825</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2.956</t>
+          <t>2657041.23979308</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2728187.58635294</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>3.085</t>
+          <t>4338306.87564331</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>3.265</t>
+          <t>4465317.52985865</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>3.506</t>
+          <t>4655325.60182466</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>4846918.17116693</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>3.666</t>
+          <t>5061139.7664442</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3.755</t>
+          <t>5170664.98828293</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3.752</t>
+          <t>5340145.86153287</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>148203.362</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>102483.591</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>103451.425</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>83729.389</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>106722.628</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>107378.973</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>107843.362</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>107148.133</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>106190.847</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>80376.956</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>106795.963</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>81380.033</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>110210.462</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>111125.848</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>109712.203</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>102758.279</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>102519.202</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>73124.252</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>105595.2</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>98057.095</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>101115.907</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>128259.289</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>129572.633</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>134298.373</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>135388.189</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>142143.785</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>144532.23</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>4465648.69239676</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>4846117.38731125</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.734</t>
+          <t>5658374.79482557</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>6288010.57685808</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>7055059.18953065</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8447583.75895968</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>9430150.62081893</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.974</t>
+          <t>9052202.33477991</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>7500636.80968186</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>7543276.9902051</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>7640546.67235728</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>8409240.62247193</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>8120824.93978851</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>7628174.46764566</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.074</t>
+          <t>8054379.89997374</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>8312252.244406</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>7909554.23395834</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>9627025.34132363</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>8893233.17400192</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>9119755.81637822</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>12001999.0255197</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>1.683</t>
+          <t>12387261.9735592</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>12897962.247761</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.797</t>
+          <t>13130097.1547974</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>13927356.6503548</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1.916</t>
+          <t>14178177.1790775</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>14921136.6436109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>450374.042</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>112009.403</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>115693.915</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>113579.325</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>135951.879</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>148760.21</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>161186.839</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>165792.517</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>153844.374</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>145245.137</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>170281.903</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>143166.866</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>150401.192</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>152030.378</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>150141.508</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>139426.447</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>132904.453</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>120597.579</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>139649.253</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>123805.309</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>135092.058</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>162402.81</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>159255.583</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>185339.516</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>168660.658</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>182873.278</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>198163.582</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-26.84</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>63.59</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>62.69</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>53.12</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>48.35</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>39.61</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>27.09</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>35.99</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>26.73</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>31.74</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>44.89</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>45.11</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>48.95</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>56.25</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>51.49</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>54.7</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>83.87</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>72.66</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>81.18</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>84.88</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>63.51</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>74.66</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>79.35</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>66.23</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>15.142</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>4.079</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>3.674</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.396</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3.485</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>3.198</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2.747</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2.974</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>3.363</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>3.082</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2.814</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2.659</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2.964</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>2.885</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2.389</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>2.552</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>2.194</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>2.186</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>6.294</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>5.143</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>6.996</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>6.932</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>7.325</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>5.411</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>7.903</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2821853.92866883</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3088035.79096244</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3691139.79345237</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3800505.81209708</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4209954.4649401</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5375109.84603957</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5302348.1381392</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>5383877.78173238</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5105411.85885166</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4712549.14588096</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5378287.34229793</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5295751.53054005</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>5023376.37316964</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>4796565.82855706</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4708474.42706477</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>5757187.03959398</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>5928680.50993965</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>5977413.37733789</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>6770248.64198032</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>7229582.93273485</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>8469114.03244872</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>8712014.36681849</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>8405839.42685243</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>8366172.73798477</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>9913449.041255</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10154725.4025397</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>9583753.72615518</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>329500427243.582</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>183234300000.019</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>188225399999.997</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>173907000000.007</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>201684299999.983</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>207681800000.008</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>213035799999.997</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>210703200000.04</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>209217500000.049</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>184073699999.948</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>210382900000.07</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>188604899999.996</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>217913099999.97</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>220612999999.924</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>219801000000.036</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>207679400000.014</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>207665600000.03</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>182694599999.956</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>216031699999.96</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>227636687740.623</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>233245291107.795</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>294241153558.04</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>294426493720.103</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>303041962755.624</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>294588389354.653</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>327978602426.702</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>329410298235.468</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>350066376996.465</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>231678300000.018</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>235382599999.989</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>218699300000.015</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>244915699999.989</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>248202200000.004</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>250068200000.006</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>247322800000.042</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>244650500000.043</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>218699599999.943</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>246757100000.072</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>223473099999.994</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>254734899999.972</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>256938999999.924</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>254869000000.041</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>241116600000.014</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>240628400000.034</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>213552299999.961</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>248582299999.962</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>243602765739.691</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>249572391606.034</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>314254631544.766</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>314360920483.009</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>323303056844.291</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>314472142191.779</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>349426941315.954</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>350740402065.107</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>148203361664.195</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>102483590853.026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>103451424727.265</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>83729388755.3488</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>106722628170.429</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>107378972961.741</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>107843361958.458</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>107148132781.07</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>106190846543.235</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>80376956108.1685</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>106795963481.431</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>81380033016.3481</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>110210461789.823</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>111125847764.404</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>109712202967.763</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>102758279168.117</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>102519202313.126</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>73124251611.7343</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>105595200043.543</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>98057095287.9337</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>101115906743.951</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>128259289478.136</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>129572633148.829</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>134298372909.318</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>135388189074.549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>142143785459.24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>144532230392.592</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>213205874.257203</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>128167499.999963</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>130145100.00001</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>118831700.000018</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>135189499.999978</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>137353100.000007</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>139174000.00003</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>139219999.999992</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>138816999.999978</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>123653999.999987</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>141572000.000006</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>127069999.999983</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>146683000.000022</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>148290000.000001</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>147644000.000035</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>142184000.000006</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>141382000.000035</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>122894999.999995</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>144752999.999993</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>141957010.986604</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>146065526.662999</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>185030568.825713</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>185632324.561415</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>191950288.082137</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>186489822.873518</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>209303585.57967</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>211026379.468675</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>200155947.04188</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>114860399.999962</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>117175500.00001</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>107185900.000019</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>123273399.999981</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>126216800.000007</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>128941000.000032</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>129086999.999992</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>128853999.999979</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>114313999.999987</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>131143000.000007</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>117488999.999984</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>136094000.000022</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>137871000.000001</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>137581000.000036</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>132355000.000006</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>131701000.000035</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>114338999.999994</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>135223999.999992</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>132543718.741931</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>136387545.287464</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>173099970.839227</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>173695782.594263</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>179721247.914089</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>174443655.026558</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>196205069.240423</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>197869497.498466</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>350066376996.465</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>231678300000.018</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>235382599999.989</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>218699300000.015</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>244915699999.989</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>248202200000.004</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>250068200000.006</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>247322800000.042</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>244650500000.043</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>218699599999.943</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>246757100000.072</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>223473099999.994</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>254734899999.972</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>256938999999.924</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>254869000000.041</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>241116600000.014</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>240628400000.034</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>213552299999.961</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>248582299999.962</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>243602765739.691</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>249572391606.034</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>314254631544.766</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>314360920483.009</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>323303056844.291</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>314472142191.779</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>349426941315.954</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>350740402065.107</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>329500427243.582</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>183234300000.019</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>188225399999.997</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>173907000000.007</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>201684299999.983</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>207681800000.008</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>213035799999.997</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>210703200000.04</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>209217500000.049</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>184073699999.948</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>210382900000.07</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>188604899999.996</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>217913099999.97</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>220612999999.924</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>219801000000.036</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>207679400000.014</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>207665600000.03</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>182694599999.956</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>216031699999.96</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>227636687740.623</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>233245291107.795</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>294241153558.04</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>294426493720.103</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>303041962755.624</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>294588389354.653</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>327978602426.702</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>329410298235.468</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>14316027.450007</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>15482370.4659364</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>18236389.4587524</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>19602052.0724249</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>21813882.7112423</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>27206266.4156403</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>28786218.1183071</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>27721943.9536544</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>24265331.3004351</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>23692651.2799394</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>25661134.4669227</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>26960137.534798</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>25874311.9871135</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>24918365.6717005</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>24219324.5582273</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>27039994.168802</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>27176170.7102962</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>30165290.2912451</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>30477348.9151133</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>31533434.9816241</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>39277760.9895018</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>39679830.8574094</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>40636341.1374142</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>41161545.932684</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>45459001.3887039</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>46211163.9990955</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>46533314.3555426</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4921276.99587354</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>5341150.50139217</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>6336426.9494057</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6916269.2275055</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>7769187.90614226</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9340715.63891083</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10361253.2747673</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9948619.40798997</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>8322979.86869321</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>8304366.89318932</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>8513417.24005019</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>9290125.46157631</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>8956069.66988413</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>8464801.19380979</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>9024640.82415185</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>9234864.96040742</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>8873619.02842426</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>10735205.0690376</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>9984270.57396883</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>10260733.9137826</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>13323148.8208155</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>13738383.9776574</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>14527796.5703106</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14771121.1889432</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>15467549.3582107</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15756482.0534959</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>16779863.4120609</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
